--- a/src/main/resources/com/cvut/fit/biopj/portniagin/semestralka/items.xlsx
+++ b/src/main/resources/com/cvut/fit/biopj/portniagin/semestralka/items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crfich\IdeaProjects\Semestralka\src\main\resources\com\cvut\fit\biopj\portniagin\semestralka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5AB303A-7750-4783-84E9-04696A091DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9461D03F-264D-485B-84DD-6C0CD3EE3AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{090F4AD3-4F98-4471-AF33-CE24C4F44B24}"/>
+    <workbookView xWindow="-28530" yWindow="4650" windowWidth="28800" windowHeight="15345" xr2:uid="{090F4AD3-4F98-4471-AF33-CE24C4F44B24}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
   <si>
     <t>itemName</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Arcane Orb</t>
   </si>
   <si>
-    <t>Soulsplitte</t>
-  </si>
-  <si>
     <t>Legendary</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>Snowflakes</t>
   </si>
   <si>
-    <t>Amethist Bow</t>
-  </si>
-  <si>
     <t>Poison Dagger</t>
   </si>
   <si>
@@ -126,9 +120,6 @@
     <t>Diamond Axe</t>
   </si>
   <si>
-    <t>Topaz Speat</t>
-  </si>
-  <si>
     <t>Emerald Sword</t>
   </si>
   <si>
@@ -183,30 +174,15 @@
     <t>Glacier</t>
   </si>
   <si>
-    <t>Frosbound</t>
-  </si>
-  <si>
-    <t>Sapfire Amulet</t>
-  </si>
-  <si>
     <t>Winter Embrace</t>
   </si>
   <si>
-    <t>Healing World</t>
-  </si>
-  <si>
     <t>Heal</t>
   </si>
   <si>
-    <t>Paladin's Hammer</t>
-  </si>
-  <si>
     <t>Divine Axe</t>
   </si>
   <si>
-    <t>Healer's Oath</t>
-  </si>
-  <si>
     <t>Lightblade</t>
   </si>
   <si>
@@ -243,7 +219,37 @@
     <t>Hook</t>
   </si>
   <si>
-    <t>Hunter's Tome</t>
+    <t>ItemSpecialEffectID</t>
+  </si>
+  <si>
+    <t>itemCost</t>
+  </si>
+  <si>
+    <t>Paladins Hammer</t>
+  </si>
+  <si>
+    <t>Healers Oath</t>
+  </si>
+  <si>
+    <t>Hunters Tome</t>
+  </si>
+  <si>
+    <t>Soulsplitter</t>
+  </si>
+  <si>
+    <t>Sapphire Amulet</t>
+  </si>
+  <si>
+    <t>Frostbound</t>
+  </si>
+  <si>
+    <t>Healing Word</t>
+  </si>
+  <si>
+    <t>Topaz Spear</t>
+  </si>
+  <si>
+    <t>Amethyst Bow</t>
   </si>
 </sst>
 </file>
@@ -598,19 +604,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A28F3E-3EC8-4738-866A-3BB12F2C350B}">
-  <dimension ref="A1:Z189"/>
+  <dimension ref="A1:AA189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="3" width="18.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="1" customWidth="1"/>
-    <col min="8" max="13" width="9.140625" style="1"/>
+    <col min="2" max="4" width="18.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="1" customWidth="1"/>
+    <col min="9" max="14" width="9.140625" style="1"/>
+    <col min="15" max="15" width="19" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -618,41 +627,44 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
@@ -662,8 +674,9 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA1" s="1"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -671,20 +684,44 @@
         <v>5</v>
       </c>
       <c r="C2" s="1">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1">
         <v>18</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>2.7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -694,8 +731,9 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA2" s="1"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -703,26 +741,44 @@
         <v>8</v>
       </c>
       <c r="C3" s="1">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>3.2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>3</v>
       </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -732,8 +788,9 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA3" s="1"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -741,20 +798,44 @@
         <v>9</v>
       </c>
       <c r="C4" s="1">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1">
         <v>10</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>3.7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -764,8 +845,9 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -776,17 +858,41 @@
         <v>25</v>
       </c>
       <c r="D5" s="1">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -796,8 +902,9 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -805,20 +912,44 @@
         <v>12</v>
       </c>
       <c r="C6" s="1">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1">
         <v>35</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>2.9</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -828,8 +959,9 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -837,35 +969,44 @@
         <v>14</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
         <v>3.3</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>3</v>
       </c>
       <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>20</v>
       </c>
       <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -875,8 +1016,9 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -884,20 +1026,44 @@
         <v>15</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
         <v>5</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -907,29 +1073,54 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1">
+        <v>25</v>
+      </c>
+      <c r="D9" s="1">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -939,32 +1130,54 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>3.3</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
         <v>3</v>
       </c>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -974,32 +1187,54 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA10" s="1"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1">
         <v>8</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>2.4</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>0.25</v>
       </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
       <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1009,35 +1244,54 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA11" s="1"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1">
         <v>8</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>3.9</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>0</v>
       </c>
       <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
         <v>2</v>
       </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
       <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1047,32 +1301,54 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA12" s="1"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1">
+        <v>25</v>
+      </c>
+      <c r="D13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>2.9</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>4</v>
       </c>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -1082,35 +1358,54 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA13" s="1"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1">
         <v>10</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <v>2.9</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
       <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1120,29 +1415,54 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA14" s="1"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1">
         <v>15</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
       <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
         <v>10</v>
       </c>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1152,29 +1472,54 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA15" s="1"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
+        <v>25</v>
+      </c>
+      <c r="D16" s="1">
         <v>20</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>17</v>
+      <c r="F16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
       </c>
       <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>3</v>
       </c>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1184,32 +1529,54 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA16" s="1"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
         <v>3.4</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
       <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>2</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>15</v>
       </c>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1219,29 +1586,54 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA17" s="1"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
       <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
         <v>2</v>
       </c>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -1251,26 +1643,54 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA18" s="1"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1">
         <v>15</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1280,29 +1700,54 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA19" s="1"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1">
+        <v>25</v>
+      </c>
+      <c r="D20" s="1">
         <v>30</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <v>3</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>0.2</v>
       </c>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -1312,29 +1757,54 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA20" s="1"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
         <v>4.8</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>17</v>
+      <c r="F21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
       </c>
       <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
         <v>5</v>
       </c>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
@@ -1344,29 +1814,54 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA21" s="1"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
         <v>3.9</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
       <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1376,29 +1871,54 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA22" s="1"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C23" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
         <v>3.7</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
       <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
         <v>5</v>
       </c>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -1408,32 +1928,54 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA23" s="1"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1">
+        <v>25</v>
+      </c>
+      <c r="D24" s="1">
         <v>5</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
         <v>4</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
       <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
         <v>3</v>
       </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
       <c r="M24" s="1">
-        <v>1</v>
-      </c>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1">
+        <v>1</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -1443,32 +1985,54 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA24" s="1"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
         <v>2.9</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
         <v>2</v>
       </c>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
@@ -1478,29 +2042,54 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA25" s="1"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C26" s="1">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1">
         <v>10</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <v>2.5</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
       <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
         <v>8</v>
       </c>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>1</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
@@ -1510,32 +2099,54 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA26" s="1"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C27" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
         <v>3.6</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
       <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
         <v>4</v>
       </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
       <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
         <v>10</v>
       </c>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -1545,29 +2156,54 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA27" s="1"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C28" s="1">
+        <v>25</v>
+      </c>
+      <c r="D28" s="1">
         <v>10</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
         <v>2.9</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>17</v>
+      <c r="F28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
       </c>
       <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
         <v>10</v>
       </c>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>1</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -1577,26 +2213,54 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA28" s="1"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C29" s="1">
+        <v>25</v>
+      </c>
+      <c r="D29" s="1">
         <v>2000</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
         <v>19</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>1</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -1606,29 +2270,54 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA29" s="1"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="1">
+        <v>25</v>
+      </c>
+      <c r="E30" s="1">
         <v>3.8</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>0.5</v>
       </c>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <v>1</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -1638,29 +2327,54 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA30" s="1"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1">
         <v>5</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="1">
+      <c r="G31" s="1">
         <v>0.5</v>
       </c>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>1</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -1670,26 +2384,54 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA31" s="1"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C32" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
         <v>5.2</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>1</v>
+      </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -1699,26 +2441,54 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA32" s="1"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C33" s="1">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1">
         <v>35</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
         <v>2.5</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>1</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -1728,29 +2498,54 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA33" s="1"/>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C34" s="1">
+        <v>25</v>
+      </c>
+      <c r="D34" s="1">
         <v>30</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>3</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="F34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="1">
         <v>0.6</v>
       </c>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>1</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -1760,26 +2555,54 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA34" s="1"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
         <v>7</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <v>1</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
@@ -1789,32 +2612,54 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA35" s="1"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C36" s="1">
+        <v>25</v>
+      </c>
+      <c r="D36" s="1">
         <v>40</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="1">
+      <c r="F36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="1">
         <v>0.2</v>
       </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
       <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
         <v>2</v>
       </c>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="O36" s="1">
+        <v>1</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -1824,29 +2669,54 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA36" s="1"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
         <v>3</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
       <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
         <v>10</v>
       </c>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>1</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
@@ -1856,29 +2726,54 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA37" s="1"/>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C38" s="1">
+        <v>25</v>
+      </c>
+      <c r="D38" s="1">
         <v>8</v>
       </c>
-      <c r="D38" s="1">
+      <c r="E38" s="1">
         <v>2.6</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
       <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
         <v>20</v>
       </c>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>1</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
@@ -1888,29 +2783,54 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA38" s="1"/>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1">
+        <v>25</v>
+      </c>
+      <c r="D39" s="1">
         <v>10</v>
       </c>
-      <c r="D39" s="1">
+      <c r="E39" s="1">
         <v>3</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
       <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
         <v>15</v>
       </c>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>1</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
@@ -1920,26 +2840,54 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA39" s="1"/>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C40" s="1">
+        <v>25</v>
+      </c>
+      <c r="D40" s="1">
         <v>15</v>
       </c>
-      <c r="D40" s="1">
+      <c r="E40" s="1">
         <v>2.9</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1">
+        <v>1</v>
+      </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
@@ -1949,29 +2897,54 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA40" s="1"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C41" s="1">
+        <v>25</v>
+      </c>
+      <c r="D41" s="1">
         <v>10</v>
       </c>
-      <c r="D41" s="1">
+      <c r="E41" s="1">
         <v>3.3</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
       <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
         <v>50</v>
       </c>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>1</v>
+      </c>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
@@ -1981,32 +2954,54 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA41" s="1"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C42" s="1">
+        <v>25</v>
+      </c>
+      <c r="D42" s="1">
         <v>15</v>
       </c>
-      <c r="D42" s="1">
+      <c r="E42" s="1">
         <v>2.9</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
       <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
         <v>10</v>
       </c>
-      <c r="M42" s="1">
+      <c r="N42" s="1">
         <v>2</v>
       </c>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="O42" s="1">
+        <v>1</v>
+      </c>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
@@ -2016,29 +3011,54 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA42" s="1"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C43" s="1">
         <v>25</v>
       </c>
       <c r="D43" s="1">
+        <v>25</v>
+      </c>
+      <c r="E43" s="1">
         <v>4.5</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>17</v>
+      <c r="F43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
       </c>
       <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
         <v>50</v>
       </c>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>1</v>
+      </c>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
@@ -2048,32 +3068,54 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA43" s="1"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C44" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
         <v>2.8</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>17</v>
+      <c r="F44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
       </c>
       <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
         <v>30</v>
       </c>
-      <c r="L44" s="1">
+      <c r="M44" s="1">
         <v>20</v>
       </c>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>1</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
@@ -2083,26 +3125,54 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA44" s="1"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C45" s="1">
+        <v>25</v>
+      </c>
+      <c r="D45" s="1">
         <v>15</v>
       </c>
-      <c r="D45" s="1">
+      <c r="E45" s="1">
         <v>3.4</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>1</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
@@ -2112,26 +3182,54 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA45" s="1"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C46" s="1">
         <v>25</v>
       </c>
       <c r="D46" s="1">
+        <v>25</v>
+      </c>
+      <c r="E46" s="1">
         <v>3.2</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>1</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
@@ -2141,29 +3239,54 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA46" s="1"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C47" s="1">
+        <v>25</v>
+      </c>
+      <c r="D47" s="1">
         <v>15</v>
       </c>
-      <c r="D47" s="1">
+      <c r="E47" s="1">
         <v>2.6</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F47" s="1">
+      <c r="G47" s="1">
         <v>0.3</v>
       </c>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>1</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
@@ -2173,29 +3296,54 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA47" s="1"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C48" s="1">
+        <v>25</v>
+      </c>
+      <c r="D48" s="1">
         <v>8</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1">
         <v>3</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
       <c r="M48" s="1">
-        <v>1</v>
-      </c>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1">
+        <v>1</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
@@ -2205,29 +3353,54 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA48" s="1"/>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C49" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>2.8</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
       <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1">
         <v>8</v>
       </c>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
+      <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1">
+        <v>1</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
@@ -2237,29 +3410,54 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA49" s="1"/>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C50" s="1">
+        <v>25</v>
+      </c>
+      <c r="D50" s="1">
         <v>20</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E50" s="1">
         <v>3.2</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <v>0.3</v>
       </c>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>1</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
@@ -2269,26 +3467,54 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA50" s="1"/>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C51" s="1">
+        <v>25</v>
+      </c>
+      <c r="D51" s="1">
         <v>12</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E51" s="1">
         <v>3.8</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>1</v>
+      </c>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
@@ -2298,29 +3524,54 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA51" s="1"/>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C52" s="1">
+        <v>25</v>
+      </c>
+      <c r="D52" s="1">
         <v>15</v>
       </c>
-      <c r="D52" s="1">
+      <c r="E52" s="1">
         <v>3.2</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="1">
+      <c r="G52" s="1">
         <v>0.3</v>
       </c>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1">
+        <v>1</v>
+      </c>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
@@ -2330,26 +3581,54 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA52" s="1"/>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C53" s="1">
         <v>25</v>
       </c>
       <c r="D53" s="1">
+        <v>25</v>
+      </c>
+      <c r="E53" s="1">
         <v>2.9</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
@@ -2359,14 +3638,9 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>53</v>
-      </c>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+      <c r="AA53" s="1"/>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
@@ -2376,14 +3650,9 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>54</v>
-      </c>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
+      <c r="AA54" s="1"/>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
@@ -2393,14 +3662,9 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
+      <c r="AA55" s="1"/>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
@@ -2410,14 +3674,9 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="AA56" s="1"/>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
@@ -2427,14 +3686,9 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
+      <c r="AA57" s="1"/>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
@@ -2444,14 +3698,9 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>58</v>
-      </c>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
+      <c r="AA58" s="1"/>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
@@ -2461,14 +3710,9 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>59</v>
-      </c>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="AA59" s="1"/>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
@@ -2478,14 +3722,9 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>60</v>
-      </c>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
+      <c r="AA60" s="1"/>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
@@ -2495,14 +3734,9 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+      <c r="AA61" s="1"/>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
@@ -2512,14 +3746,9 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>62</v>
-      </c>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
+      <c r="AA62" s="1"/>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
@@ -2529,14 +3758,9 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
+      <c r="AA63" s="1"/>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
@@ -2546,14 +3770,9 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>64</v>
-      </c>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
+      <c r="AA64" s="1"/>
+    </row>
+    <row r="65" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
@@ -2563,14 +3782,9 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>65</v>
-      </c>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
+      <c r="AA65" s="1"/>
+    </row>
+    <row r="66" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
@@ -2580,14 +3794,9 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>66</v>
-      </c>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
+      <c r="AA66" s="1"/>
+    </row>
+    <row r="67" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
@@ -2597,14 +3806,9 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>67</v>
-      </c>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
+      <c r="AA67" s="1"/>
+    </row>
+    <row r="68" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
@@ -2614,14 +3818,9 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>68</v>
-      </c>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
+      <c r="AA68" s="1"/>
+    </row>
+    <row r="69" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
@@ -2631,14 +3830,9 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>69</v>
-      </c>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
+      <c r="AA69" s="1"/>
+    </row>
+    <row r="70" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="1"/>
@@ -2648,14 +3842,9 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>70</v>
-      </c>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
+      <c r="AA70" s="1"/>
+    </row>
+    <row r="71" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
@@ -2665,14 +3854,9 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>71</v>
-      </c>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
+      <c r="AA71" s="1"/>
+    </row>
+    <row r="72" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
       <c r="T72" s="1"/>
@@ -2682,14 +3866,9 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>72</v>
-      </c>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
+      <c r="AA72" s="1"/>
+    </row>
+    <row r="73" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
@@ -2699,14 +3878,9 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>73</v>
-      </c>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
+      <c r="AA73" s="1"/>
+    </row>
+    <row r="74" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
@@ -2716,14 +3890,9 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>74</v>
-      </c>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
+      <c r="AA74" s="1"/>
+    </row>
+    <row r="75" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
@@ -2733,14 +3902,9 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>75</v>
-      </c>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
+      <c r="AA75" s="1"/>
+    </row>
+    <row r="76" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
@@ -2750,14 +3914,9 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>76</v>
-      </c>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
+      <c r="AA76" s="1"/>
+    </row>
+    <row r="77" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
@@ -2767,14 +3926,9 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>77</v>
-      </c>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
+      <c r="AA77" s="1"/>
+    </row>
+    <row r="78" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
@@ -2784,14 +3938,9 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>78</v>
-      </c>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
+      <c r="AA78" s="1"/>
+    </row>
+    <row r="79" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
@@ -2801,14 +3950,9 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>79</v>
-      </c>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
-      <c r="Q80" s="1"/>
+      <c r="AA79" s="1"/>
+    </row>
+    <row r="80" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
@@ -2818,14 +3962,9 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>80</v>
-      </c>
-      <c r="O81" s="1"/>
-      <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
+      <c r="AA80" s="1"/>
+    </row>
+    <row r="81" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
       <c r="T81" s="1"/>
@@ -2835,14 +3974,9 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>81</v>
-      </c>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
+      <c r="AA81" s="1"/>
+    </row>
+    <row r="82" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
       <c r="T82" s="1"/>
@@ -2852,14 +3986,9 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>82</v>
-      </c>
-      <c r="O83" s="1"/>
-      <c r="P83" s="1"/>
-      <c r="Q83" s="1"/>
+      <c r="AA82" s="1"/>
+    </row>
+    <row r="83" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
       <c r="T83" s="1"/>
@@ -2869,14 +3998,9 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>83</v>
-      </c>
-      <c r="O84" s="1"/>
-      <c r="P84" s="1"/>
-      <c r="Q84" s="1"/>
+      <c r="AA83" s="1"/>
+    </row>
+    <row r="84" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
       <c r="T84" s="1"/>
@@ -2886,14 +4010,9 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>84</v>
-      </c>
-      <c r="O85" s="1"/>
-      <c r="P85" s="1"/>
-      <c r="Q85" s="1"/>
+      <c r="AA84" s="1"/>
+    </row>
+    <row r="85" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
       <c r="T85" s="1"/>
@@ -2903,14 +4022,9 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>85</v>
-      </c>
-      <c r="O86" s="1"/>
-      <c r="P86" s="1"/>
-      <c r="Q86" s="1"/>
+      <c r="AA85" s="1"/>
+    </row>
+    <row r="86" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
@@ -2920,14 +4034,9 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>86</v>
-      </c>
-      <c r="O87" s="1"/>
-      <c r="P87" s="1"/>
-      <c r="Q87" s="1"/>
+      <c r="AA86" s="1"/>
+    </row>
+    <row r="87" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
       <c r="T87" s="1"/>
@@ -2937,14 +4046,9 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>87</v>
-      </c>
-      <c r="O88" s="1"/>
-      <c r="P88" s="1"/>
-      <c r="Q88" s="1"/>
+      <c r="AA87" s="1"/>
+    </row>
+    <row r="88" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
       <c r="T88" s="1"/>
@@ -2954,14 +4058,9 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>88</v>
-      </c>
-      <c r="O89" s="1"/>
-      <c r="P89" s="1"/>
-      <c r="Q89" s="1"/>
+      <c r="AA88" s="1"/>
+    </row>
+    <row r="89" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
       <c r="T89" s="1"/>
@@ -2971,14 +4070,9 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>89</v>
-      </c>
-      <c r="O90" s="1"/>
-      <c r="P90" s="1"/>
-      <c r="Q90" s="1"/>
+      <c r="AA89" s="1"/>
+    </row>
+    <row r="90" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
       <c r="T90" s="1"/>
@@ -2988,14 +4082,9 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>90</v>
-      </c>
-      <c r="O91" s="1"/>
-      <c r="P91" s="1"/>
-      <c r="Q91" s="1"/>
+      <c r="AA90" s="1"/>
+    </row>
+    <row r="91" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
       <c r="T91" s="1"/>
@@ -3005,14 +4094,9 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>91</v>
-      </c>
-      <c r="O92" s="1"/>
-      <c r="P92" s="1"/>
-      <c r="Q92" s="1"/>
+      <c r="AA91" s="1"/>
+    </row>
+    <row r="92" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
       <c r="T92" s="1"/>
@@ -3022,14 +4106,9 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>92</v>
-      </c>
-      <c r="O93" s="1"/>
-      <c r="P93" s="1"/>
-      <c r="Q93" s="1"/>
+      <c r="AA92" s="1"/>
+    </row>
+    <row r="93" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
       <c r="T93" s="1"/>
@@ -3039,14 +4118,9 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>93</v>
-      </c>
-      <c r="O94" s="1"/>
-      <c r="P94" s="1"/>
-      <c r="Q94" s="1"/>
+      <c r="AA93" s="1"/>
+    </row>
+    <row r="94" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
       <c r="T94" s="1"/>
@@ -3056,14 +4130,9 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>94</v>
-      </c>
-      <c r="O95" s="1"/>
-      <c r="P95" s="1"/>
-      <c r="Q95" s="1"/>
+      <c r="AA94" s="1"/>
+    </row>
+    <row r="95" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
       <c r="T95" s="1"/>
@@ -3073,14 +4142,9 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>95</v>
-      </c>
-      <c r="O96" s="1"/>
-      <c r="P96" s="1"/>
-      <c r="Q96" s="1"/>
+      <c r="AA95" s="1"/>
+    </row>
+    <row r="96" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
       <c r="T96" s="1"/>
@@ -3090,14 +4154,9 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>96</v>
-      </c>
-      <c r="O97" s="1"/>
-      <c r="P97" s="1"/>
-      <c r="Q97" s="1"/>
+      <c r="AA96" s="1"/>
+    </row>
+    <row r="97" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
       <c r="T97" s="1"/>
@@ -3107,14 +4166,9 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>97</v>
-      </c>
-      <c r="O98" s="1"/>
-      <c r="P98" s="1"/>
-      <c r="Q98" s="1"/>
+      <c r="AA97" s="1"/>
+    </row>
+    <row r="98" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
       <c r="T98" s="1"/>
@@ -3124,14 +4178,9 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>98</v>
-      </c>
-      <c r="O99" s="1"/>
-      <c r="P99" s="1"/>
-      <c r="Q99" s="1"/>
+      <c r="AA98" s="1"/>
+    </row>
+    <row r="99" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
       <c r="T99" s="1"/>
@@ -3141,14 +4190,9 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>99</v>
-      </c>
-      <c r="O100" s="1"/>
-      <c r="P100" s="1"/>
-      <c r="Q100" s="1"/>
+      <c r="AA99" s="1"/>
+    </row>
+    <row r="100" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
       <c r="T100" s="1"/>
@@ -3158,14 +4202,9 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>100</v>
-      </c>
-      <c r="O101" s="1"/>
-      <c r="P101" s="1"/>
-      <c r="Q101" s="1"/>
+      <c r="AA100" s="1"/>
+    </row>
+    <row r="101" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
       <c r="T101" s="1"/>
@@ -3175,14 +4214,9 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>101</v>
-      </c>
-      <c r="O102" s="1"/>
-      <c r="P102" s="1"/>
-      <c r="Q102" s="1"/>
+      <c r="AA101" s="1"/>
+    </row>
+    <row r="102" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
       <c r="T102" s="1"/>
@@ -3192,14 +4226,9 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
-        <v>102</v>
-      </c>
-      <c r="O103" s="1"/>
-      <c r="P103" s="1"/>
-      <c r="Q103" s="1"/>
+      <c r="AA102" s="1"/>
+    </row>
+    <row r="103" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
       <c r="T103" s="1"/>
@@ -3209,14 +4238,9 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
-        <v>103</v>
-      </c>
-      <c r="O104" s="1"/>
-      <c r="P104" s="1"/>
-      <c r="Q104" s="1"/>
+      <c r="AA103" s="1"/>
+    </row>
+    <row r="104" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
       <c r="T104" s="1"/>
@@ -3226,14 +4250,9 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
-        <v>104</v>
-      </c>
-      <c r="O105" s="1"/>
-      <c r="P105" s="1"/>
-      <c r="Q105" s="1"/>
+      <c r="AA104" s="1"/>
+    </row>
+    <row r="105" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
       <c r="T105" s="1"/>
@@ -3243,14 +4262,9 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>105</v>
-      </c>
-      <c r="O106" s="1"/>
-      <c r="P106" s="1"/>
-      <c r="Q106" s="1"/>
+      <c r="AA105" s="1"/>
+    </row>
+    <row r="106" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
       <c r="T106" s="1"/>
@@ -3260,14 +4274,9 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
-        <v>106</v>
-      </c>
-      <c r="O107" s="1"/>
-      <c r="P107" s="1"/>
-      <c r="Q107" s="1"/>
+      <c r="AA106" s="1"/>
+    </row>
+    <row r="107" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
       <c r="T107" s="1"/>
@@ -3277,14 +4286,9 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>107</v>
-      </c>
-      <c r="O108" s="1"/>
-      <c r="P108" s="1"/>
-      <c r="Q108" s="1"/>
+      <c r="AA107" s="1"/>
+    </row>
+    <row r="108" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
       <c r="T108" s="1"/>
@@ -3294,14 +4298,9 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
-        <v>108</v>
-      </c>
-      <c r="O109" s="1"/>
-      <c r="P109" s="1"/>
-      <c r="Q109" s="1"/>
+      <c r="AA108" s="1"/>
+    </row>
+    <row r="109" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
@@ -3311,14 +4310,9 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>109</v>
-      </c>
-      <c r="O110" s="1"/>
-      <c r="P110" s="1"/>
-      <c r="Q110" s="1"/>
+      <c r="AA109" s="1"/>
+    </row>
+    <row r="110" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
       <c r="T110" s="1"/>
@@ -3328,14 +4322,9 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>110</v>
-      </c>
-      <c r="O111" s="1"/>
-      <c r="P111" s="1"/>
-      <c r="Q111" s="1"/>
+      <c r="AA110" s="1"/>
+    </row>
+    <row r="111" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
       <c r="T111" s="1"/>
@@ -3345,14 +4334,9 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
-        <v>111</v>
-      </c>
-      <c r="O112" s="1"/>
-      <c r="P112" s="1"/>
-      <c r="Q112" s="1"/>
+      <c r="AA111" s="1"/>
+    </row>
+    <row r="112" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
@@ -3362,14 +4346,9 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>112</v>
-      </c>
-      <c r="O113" s="1"/>
-      <c r="P113" s="1"/>
-      <c r="Q113" s="1"/>
+      <c r="AA112" s="1"/>
+    </row>
+    <row r="113" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
@@ -3379,14 +4358,9 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>113</v>
-      </c>
-      <c r="O114" s="1"/>
-      <c r="P114" s="1"/>
-      <c r="Q114" s="1"/>
+      <c r="AA113" s="1"/>
+    </row>
+    <row r="114" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
       <c r="T114" s="1"/>
@@ -3396,14 +4370,9 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>114</v>
-      </c>
-      <c r="O115" s="1"/>
-      <c r="P115" s="1"/>
-      <c r="Q115" s="1"/>
+      <c r="AA114" s="1"/>
+    </row>
+    <row r="115" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
       <c r="T115" s="1"/>
@@ -3413,14 +4382,9 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>115</v>
-      </c>
-      <c r="O116" s="1"/>
-      <c r="P116" s="1"/>
-      <c r="Q116" s="1"/>
+      <c r="AA115" s="1"/>
+    </row>
+    <row r="116" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
       <c r="T116" s="1"/>
@@ -3430,14 +4394,9 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>116</v>
-      </c>
-      <c r="O117" s="1"/>
-      <c r="P117" s="1"/>
-      <c r="Q117" s="1"/>
+      <c r="AA116" s="1"/>
+    </row>
+    <row r="117" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
       <c r="T117" s="1"/>
@@ -3447,14 +4406,9 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>117</v>
-      </c>
-      <c r="O118" s="1"/>
-      <c r="P118" s="1"/>
-      <c r="Q118" s="1"/>
+      <c r="AA117" s="1"/>
+    </row>
+    <row r="118" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
       <c r="T118" s="1"/>
@@ -3464,14 +4418,9 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>118</v>
-      </c>
-      <c r="O119" s="1"/>
-      <c r="P119" s="1"/>
-      <c r="Q119" s="1"/>
+      <c r="AA118" s="1"/>
+    </row>
+    <row r="119" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
       <c r="T119" s="1"/>
@@ -3481,14 +4430,9 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
-        <v>119</v>
-      </c>
-      <c r="O120" s="1"/>
-      <c r="P120" s="1"/>
-      <c r="Q120" s="1"/>
+      <c r="AA119" s="1"/>
+    </row>
+    <row r="120" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
       <c r="T120" s="1"/>
@@ -3498,14 +4442,9 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
-        <v>120</v>
-      </c>
-      <c r="O121" s="1"/>
-      <c r="P121" s="1"/>
-      <c r="Q121" s="1"/>
+      <c r="AA120" s="1"/>
+    </row>
+    <row r="121" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
       <c r="T121" s="1"/>
@@ -3515,14 +4454,9 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
-    </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
-        <v>121</v>
-      </c>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
+      <c r="AA121" s="1"/>
+    </row>
+    <row r="122" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
       <c r="T122" s="1"/>
@@ -3532,14 +4466,9 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
-    </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
-        <v>122</v>
-      </c>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
+      <c r="AA122" s="1"/>
+    </row>
+    <row r="123" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
       <c r="T123" s="1"/>
@@ -3549,14 +4478,9 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
-    </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>123</v>
-      </c>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1"/>
-      <c r="Q124" s="1"/>
+      <c r="AA123" s="1"/>
+    </row>
+    <row r="124" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
       <c r="T124" s="1"/>
@@ -3566,14 +4490,9 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
-    </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>124</v>
-      </c>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
+      <c r="AA124" s="1"/>
+    </row>
+    <row r="125" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
       <c r="T125" s="1"/>
@@ -3583,14 +4502,9 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
-    </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
-        <v>125</v>
-      </c>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
+      <c r="AA125" s="1"/>
+    </row>
+    <row r="126" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
       <c r="T126" s="1"/>
@@ -3600,14 +4514,9 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
-    </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>126</v>
-      </c>
-      <c r="O127" s="1"/>
-      <c r="P127" s="1"/>
-      <c r="Q127" s="1"/>
+      <c r="AA126" s="1"/>
+    </row>
+    <row r="127" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
       <c r="T127" s="1"/>
@@ -3617,14 +4526,9 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
-    </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
-        <v>127</v>
-      </c>
-      <c r="O128" s="1"/>
-      <c r="P128" s="1"/>
-      <c r="Q128" s="1"/>
+      <c r="AA127" s="1"/>
+    </row>
+    <row r="128" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
       <c r="T128" s="1"/>
@@ -3634,14 +4538,9 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
-    </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
-        <v>128</v>
-      </c>
-      <c r="O129" s="1"/>
-      <c r="P129" s="1"/>
-      <c r="Q129" s="1"/>
+      <c r="AA128" s="1"/>
+    </row>
+    <row r="129" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
       <c r="T129" s="1"/>
@@ -3651,14 +4550,9 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
-    </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
-        <v>129</v>
-      </c>
-      <c r="O130" s="1"/>
-      <c r="P130" s="1"/>
-      <c r="Q130" s="1"/>
+      <c r="AA129" s="1"/>
+    </row>
+    <row r="130" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
       <c r="T130" s="1"/>
@@ -3668,14 +4562,9 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
-    </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>130</v>
-      </c>
-      <c r="O131" s="1"/>
-      <c r="P131" s="1"/>
-      <c r="Q131" s="1"/>
+      <c r="AA130" s="1"/>
+    </row>
+    <row r="131" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
       <c r="T131" s="1"/>
@@ -3685,14 +4574,9 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
-    </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
-        <v>131</v>
-      </c>
-      <c r="O132" s="1"/>
-      <c r="P132" s="1"/>
-      <c r="Q132" s="1"/>
+      <c r="AA131" s="1"/>
+    </row>
+    <row r="132" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
       <c r="T132" s="1"/>
@@ -3702,14 +4586,9 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
-    </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
-        <v>132</v>
-      </c>
-      <c r="O133" s="1"/>
-      <c r="P133" s="1"/>
-      <c r="Q133" s="1"/>
+      <c r="AA132" s="1"/>
+    </row>
+    <row r="133" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="1"/>
@@ -3719,14 +4598,9 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
-    </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
-        <v>133</v>
-      </c>
-      <c r="O134" s="1"/>
-      <c r="P134" s="1"/>
-      <c r="Q134" s="1"/>
+      <c r="AA133" s="1"/>
+    </row>
+    <row r="134" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
       <c r="T134" s="1"/>
@@ -3736,14 +4610,9 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
-    </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
-        <v>134</v>
-      </c>
-      <c r="O135" s="1"/>
-      <c r="P135" s="1"/>
-      <c r="Q135" s="1"/>
+      <c r="AA134" s="1"/>
+    </row>
+    <row r="135" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
       <c r="T135" s="1"/>
@@ -3753,14 +4622,9 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
-        <v>135</v>
-      </c>
-      <c r="O136" s="1"/>
-      <c r="P136" s="1"/>
-      <c r="Q136" s="1"/>
+      <c r="AA135" s="1"/>
+    </row>
+    <row r="136" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
@@ -3770,14 +4634,9 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
-    </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A137" s="1">
-        <v>136</v>
-      </c>
-      <c r="O137" s="1"/>
-      <c r="P137" s="1"/>
-      <c r="Q137" s="1"/>
+      <c r="AA136" s="1"/>
+    </row>
+    <row r="137" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
@@ -3787,14 +4646,9 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
-    </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A138" s="1">
-        <v>137</v>
-      </c>
-      <c r="O138" s="1"/>
-      <c r="P138" s="1"/>
-      <c r="Q138" s="1"/>
+      <c r="AA137" s="1"/>
+    </row>
+    <row r="138" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
@@ -3804,14 +4658,9 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
-    </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A139" s="1">
-        <v>138</v>
-      </c>
-      <c r="O139" s="1"/>
-      <c r="P139" s="1"/>
-      <c r="Q139" s="1"/>
+      <c r="AA138" s="1"/>
+    </row>
+    <row r="139" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
@@ -3821,14 +4670,9 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
-    </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A140" s="1">
-        <v>139</v>
-      </c>
-      <c r="O140" s="1"/>
-      <c r="P140" s="1"/>
-      <c r="Q140" s="1"/>
+      <c r="AA139" s="1"/>
+    </row>
+    <row r="140" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
@@ -3838,14 +4682,9 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A141" s="1">
-        <v>140</v>
-      </c>
-      <c r="O141" s="1"/>
-      <c r="P141" s="1"/>
-      <c r="Q141" s="1"/>
+      <c r="AA140" s="1"/>
+    </row>
+    <row r="141" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
@@ -3855,14 +4694,9 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
-    </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A142" s="1">
-        <v>141</v>
-      </c>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1"/>
-      <c r="Q142" s="1"/>
+      <c r="AA141" s="1"/>
+    </row>
+    <row r="142" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
@@ -3872,11 +4706,9 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
-    </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="O143" s="1"/>
-      <c r="P143" s="1"/>
-      <c r="Q143" s="1"/>
+      <c r="AA142" s="1"/>
+    </row>
+    <row r="143" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
       <c r="T143" s="1"/>
@@ -3886,11 +4718,9 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
-    </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
+      <c r="AA143" s="1"/>
+    </row>
+    <row r="144" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
@@ -3900,11 +4730,9 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
-    </row>
-    <row r="145" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O145" s="1"/>
-      <c r="P145" s="1"/>
-      <c r="Q145" s="1"/>
+      <c r="AA144" s="1"/>
+    </row>
+    <row r="145" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
@@ -3914,11 +4742,9 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
-    </row>
-    <row r="146" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O146" s="1"/>
-      <c r="P146" s="1"/>
-      <c r="Q146" s="1"/>
+      <c r="AA145" s="1"/>
+    </row>
+    <row r="146" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -3928,11 +4754,9 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
-    </row>
-    <row r="147" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O147" s="1"/>
-      <c r="P147" s="1"/>
-      <c r="Q147" s="1"/>
+      <c r="AA146" s="1"/>
+    </row>
+    <row r="147" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
@@ -3942,11 +4766,9 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
-    </row>
-    <row r="148" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O148" s="1"/>
-      <c r="P148" s="1"/>
-      <c r="Q148" s="1"/>
+      <c r="AA147" s="1"/>
+    </row>
+    <row r="148" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
@@ -3956,11 +4778,9 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
-    </row>
-    <row r="149" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
-      <c r="Q149" s="1"/>
+      <c r="AA148" s="1"/>
+    </row>
+    <row r="149" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
@@ -3970,11 +4790,9 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
-    </row>
-    <row r="150" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O150" s="1"/>
-      <c r="P150" s="1"/>
-      <c r="Q150" s="1"/>
+      <c r="AA149" s="1"/>
+    </row>
+    <row r="150" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
       <c r="T150" s="1"/>
@@ -3984,11 +4802,9 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
-    </row>
-    <row r="151" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O151" s="1"/>
-      <c r="P151" s="1"/>
-      <c r="Q151" s="1"/>
+      <c r="AA150" s="1"/>
+    </row>
+    <row r="151" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
       <c r="T151" s="1"/>
@@ -3998,11 +4814,9 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
-    </row>
-    <row r="152" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O152" s="1"/>
-      <c r="P152" s="1"/>
-      <c r="Q152" s="1"/>
+      <c r="AA151" s="1"/>
+    </row>
+    <row r="152" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
       <c r="T152" s="1"/>
@@ -4012,11 +4826,9 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
-    </row>
-    <row r="153" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O153" s="1"/>
-      <c r="P153" s="1"/>
-      <c r="Q153" s="1"/>
+      <c r="AA152" s="1"/>
+    </row>
+    <row r="153" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
       <c r="T153" s="1"/>
@@ -4026,11 +4838,9 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
-    </row>
-    <row r="154" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O154" s="1"/>
-      <c r="P154" s="1"/>
-      <c r="Q154" s="1"/>
+      <c r="AA153" s="1"/>
+    </row>
+    <row r="154" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
       <c r="T154" s="1"/>
@@ -4040,11 +4850,9 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
-    </row>
-    <row r="155" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O155" s="1"/>
-      <c r="P155" s="1"/>
-      <c r="Q155" s="1"/>
+      <c r="AA154" s="1"/>
+    </row>
+    <row r="155" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
       <c r="T155" s="1"/>
@@ -4054,11 +4862,9 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
-    </row>
-    <row r="156" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O156" s="1"/>
-      <c r="P156" s="1"/>
-      <c r="Q156" s="1"/>
+      <c r="AA155" s="1"/>
+    </row>
+    <row r="156" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
@@ -4068,11 +4874,9 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
-    </row>
-    <row r="157" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O157" s="1"/>
-      <c r="P157" s="1"/>
-      <c r="Q157" s="1"/>
+      <c r="AA156" s="1"/>
+    </row>
+    <row r="157" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
       <c r="T157" s="1"/>
@@ -4082,11 +4886,9 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
-    </row>
-    <row r="158" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O158" s="1"/>
-      <c r="P158" s="1"/>
-      <c r="Q158" s="1"/>
+      <c r="AA157" s="1"/>
+    </row>
+    <row r="158" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
       <c r="T158" s="1"/>
@@ -4096,11 +4898,9 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
-    </row>
-    <row r="159" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O159" s="1"/>
-      <c r="P159" s="1"/>
-      <c r="Q159" s="1"/>
+      <c r="AA158" s="1"/>
+    </row>
+    <row r="159" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
       <c r="T159" s="1"/>
@@ -4110,11 +4910,9 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
-    </row>
-    <row r="160" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O160" s="1"/>
-      <c r="P160" s="1"/>
-      <c r="Q160" s="1"/>
+      <c r="AA159" s="1"/>
+    </row>
+    <row r="160" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
       <c r="T160" s="1"/>
@@ -4124,11 +4922,9 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
-    </row>
-    <row r="161" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O161" s="1"/>
-      <c r="P161" s="1"/>
-      <c r="Q161" s="1"/>
+      <c r="AA160" s="1"/>
+    </row>
+    <row r="161" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
       <c r="T161" s="1"/>
@@ -4138,11 +4934,9 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
-    </row>
-    <row r="162" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O162" s="1"/>
-      <c r="P162" s="1"/>
-      <c r="Q162" s="1"/>
+      <c r="AA161" s="1"/>
+    </row>
+    <row r="162" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
       <c r="T162" s="1"/>
@@ -4152,11 +4946,9 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
-    </row>
-    <row r="163" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O163" s="1"/>
-      <c r="P163" s="1"/>
-      <c r="Q163" s="1"/>
+      <c r="AA162" s="1"/>
+    </row>
+    <row r="163" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
       <c r="T163" s="1"/>
@@ -4166,11 +4958,9 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
-    </row>
-    <row r="164" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O164" s="1"/>
-      <c r="P164" s="1"/>
-      <c r="Q164" s="1"/>
+      <c r="AA163" s="1"/>
+    </row>
+    <row r="164" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
       <c r="T164" s="1"/>
@@ -4180,11 +4970,9 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
-    </row>
-    <row r="165" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O165" s="1"/>
-      <c r="P165" s="1"/>
-      <c r="Q165" s="1"/>
+      <c r="AA164" s="1"/>
+    </row>
+    <row r="165" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
       <c r="T165" s="1"/>
@@ -4194,11 +4982,9 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
-    </row>
-    <row r="166" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O166" s="1"/>
-      <c r="P166" s="1"/>
-      <c r="Q166" s="1"/>
+      <c r="AA165" s="1"/>
+    </row>
+    <row r="166" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
       <c r="T166" s="1"/>
@@ -4208,11 +4994,9 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
-    </row>
-    <row r="167" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O167" s="1"/>
-      <c r="P167" s="1"/>
-      <c r="Q167" s="1"/>
+      <c r="AA166" s="1"/>
+    </row>
+    <row r="167" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
@@ -4222,11 +5006,9 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
-    </row>
-    <row r="168" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O168" s="1"/>
-      <c r="P168" s="1"/>
-      <c r="Q168" s="1"/>
+      <c r="AA167" s="1"/>
+    </row>
+    <row r="168" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
@@ -4236,11 +5018,9 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
-    </row>
-    <row r="169" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O169" s="1"/>
-      <c r="P169" s="1"/>
-      <c r="Q169" s="1"/>
+      <c r="AA168" s="1"/>
+    </row>
+    <row r="169" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
@@ -4250,11 +5030,9 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
-    </row>
-    <row r="170" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O170" s="1"/>
-      <c r="P170" s="1"/>
-      <c r="Q170" s="1"/>
+      <c r="AA169" s="1"/>
+    </row>
+    <row r="170" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
@@ -4264,11 +5042,9 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
-    </row>
-    <row r="171" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O171" s="1"/>
-      <c r="P171" s="1"/>
-      <c r="Q171" s="1"/>
+      <c r="AA170" s="1"/>
+    </row>
+    <row r="171" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
@@ -4278,11 +5054,9 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
-    </row>
-    <row r="172" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O172" s="1"/>
-      <c r="P172" s="1"/>
-      <c r="Q172" s="1"/>
+      <c r="AA171" s="1"/>
+    </row>
+    <row r="172" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
@@ -4292,11 +5066,9 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
-    </row>
-    <row r="173" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O173" s="1"/>
-      <c r="P173" s="1"/>
-      <c r="Q173" s="1"/>
+      <c r="AA172" s="1"/>
+    </row>
+    <row r="173" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
       <c r="T173" s="1"/>
@@ -4306,11 +5078,9 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
-    </row>
-    <row r="174" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O174" s="1"/>
-      <c r="P174" s="1"/>
-      <c r="Q174" s="1"/>
+      <c r="AA173" s="1"/>
+    </row>
+    <row r="174" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
       <c r="T174" s="1"/>
@@ -4320,11 +5090,9 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
-    </row>
-    <row r="175" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O175" s="1"/>
-      <c r="P175" s="1"/>
-      <c r="Q175" s="1"/>
+      <c r="AA174" s="1"/>
+    </row>
+    <row r="175" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
       <c r="T175" s="1"/>
@@ -4334,11 +5102,9 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
-    </row>
-    <row r="176" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O176" s="1"/>
-      <c r="P176" s="1"/>
-      <c r="Q176" s="1"/>
+      <c r="AA175" s="1"/>
+    </row>
+    <row r="176" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
       <c r="T176" s="1"/>
@@ -4348,11 +5114,9 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
-    </row>
-    <row r="177" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O177" s="1"/>
-      <c r="P177" s="1"/>
-      <c r="Q177" s="1"/>
+      <c r="AA176" s="1"/>
+    </row>
+    <row r="177" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
       <c r="T177" s="1"/>
@@ -4362,11 +5126,9 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
-    </row>
-    <row r="178" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O178" s="1"/>
-      <c r="P178" s="1"/>
-      <c r="Q178" s="1"/>
+      <c r="AA177" s="1"/>
+    </row>
+    <row r="178" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
       <c r="T178" s="1"/>
@@ -4376,11 +5138,9 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
-    </row>
-    <row r="179" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O179" s="1"/>
-      <c r="P179" s="1"/>
-      <c r="Q179" s="1"/>
+      <c r="AA178" s="1"/>
+    </row>
+    <row r="179" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
       <c r="T179" s="1"/>
@@ -4390,11 +5150,9 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
-    </row>
-    <row r="180" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O180" s="1"/>
-      <c r="P180" s="1"/>
-      <c r="Q180" s="1"/>
+      <c r="AA179" s="1"/>
+    </row>
+    <row r="180" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
       <c r="T180" s="1"/>
@@ -4404,11 +5162,9 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
-    </row>
-    <row r="181" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O181" s="1"/>
-      <c r="P181" s="1"/>
-      <c r="Q181" s="1"/>
+      <c r="AA180" s="1"/>
+    </row>
+    <row r="181" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -4418,11 +5174,9 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
-    </row>
-    <row r="182" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O182" s="1"/>
-      <c r="P182" s="1"/>
-      <c r="Q182" s="1"/>
+      <c r="AA181" s="1"/>
+    </row>
+    <row r="182" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
       <c r="T182" s="1"/>
@@ -4432,11 +5186,9 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
-    </row>
-    <row r="183" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O183" s="1"/>
-      <c r="P183" s="1"/>
-      <c r="Q183" s="1"/>
+      <c r="AA182" s="1"/>
+    </row>
+    <row r="183" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
@@ -4446,11 +5198,9 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
-    </row>
-    <row r="184" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O184" s="1"/>
-      <c r="P184" s="1"/>
-      <c r="Q184" s="1"/>
+      <c r="AA183" s="1"/>
+    </row>
+    <row r="184" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
@@ -4460,11 +5210,9 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
-    </row>
-    <row r="185" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O185" s="1"/>
-      <c r="P185" s="1"/>
-      <c r="Q185" s="1"/>
+      <c r="AA184" s="1"/>
+    </row>
+    <row r="185" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
       <c r="T185" s="1"/>
@@ -4474,11 +5222,9 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
-    </row>
-    <row r="186" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O186" s="1"/>
-      <c r="P186" s="1"/>
-      <c r="Q186" s="1"/>
+      <c r="AA185" s="1"/>
+    </row>
+    <row r="186" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
       <c r="T186" s="1"/>
@@ -4488,11 +5234,9 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
-    </row>
-    <row r="187" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O187" s="1"/>
-      <c r="P187" s="1"/>
-      <c r="Q187" s="1"/>
+      <c r="AA186" s="1"/>
+    </row>
+    <row r="187" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
@@ -4502,11 +5246,9 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
-    </row>
-    <row r="188" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O188" s="1"/>
-      <c r="P188" s="1"/>
-      <c r="Q188" s="1"/>
+      <c r="AA187" s="1"/>
+    </row>
+    <row r="188" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
       <c r="T188" s="1"/>
@@ -4516,11 +5258,9 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
-    </row>
-    <row r="189" spans="15:26" x14ac:dyDescent="0.25">
-      <c r="O189" s="1"/>
-      <c r="P189" s="1"/>
-      <c r="Q189" s="1"/>
+      <c r="AA188" s="1"/>
+    </row>
+    <row r="189" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
       <c r="T189" s="1"/>
@@ -4530,6 +5270,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
+      <c r="AA189" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
